--- a/one down/普物實驗/實驗資料夾範例/E24146107_王翊權_預報11_表格.xlsx
+++ b/one down/普物實驗/實驗資料夾範例/E24146107_王翊權_預報11_表格.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\school\one up\普物實驗\Lab11 彈簧縱波的駐波實驗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\school\one down\普物實驗\實驗資料夾範例\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F320BB-D1CC-4608-99E4-150E3C144FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75082E36-92E6-46D9-9C4A-8A6A6D30226D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="18648" windowHeight="11784" activeTab="1" xr2:uid="{DB1FF5BB-3E16-44F6-8EBE-091011F52E70}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{DB1FF5BB-3E16-44F6-8EBE-091011F52E70}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
-    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,65 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
-  <si>
-    <t>#1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#3</t>
-  </si>
-  <si>
-    <t>#4</t>
-  </si>
-  <si>
-    <t>#5</t>
-  </si>
-  <si>
-    <t>L_4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\frac{L}{\lambda}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>彈簧質量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掛重</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伸長量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>k</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>原長</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -125,27 +66,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -158,7 +84,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -495,239 +421,185 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3419739-BEEB-4B53-8EC5-6DC56A0166CA}">
-  <dimension ref="A4:G16"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A3:H19"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="1">
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" s="1"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>24.5</v>
-      </c>
-      <c r="D7" s="1">
-        <v>28</v>
-      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>11.5</v>
-      </c>
-      <c r="D8" s="1">
-        <v>12.5</v>
-      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="1">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" s="1"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0221AA1A-1987-4F82-96E4-FD9B3B087DF3}">
-  <dimension ref="A2:J11"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1">
-        <v>150</v>
-      </c>
-      <c r="D3" s="1">
-        <v>200</v>
-      </c>
-      <c r="E3" s="1">
-        <v>250</v>
-      </c>
-      <c r="F3" s="1">
-        <v>300</v>
-      </c>
-      <c r="G3" s="1">
-        <v>350</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="I4" s="1">
-        <v>10</v>
-      </c>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="1">
-        <v>10</v>
-      </c>
-      <c r="D10" s="1">
-        <v>20</v>
-      </c>
-      <c r="E10" s="1">
-        <v>30</v>
-      </c>
-      <c r="F10" s="1">
-        <v>40</v>
-      </c>
-      <c r="G10" s="1">
-        <v>50</v>
-      </c>
-      <c r="I10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="J11" s="1"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>